--- a/docs/reviews/2026-10-18-b2-tarot-copy-review.xlsx
+++ b/docs/reviews/2026-10-18-b2-tarot-copy-review.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Cụm từ B2-1, B2-3" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Nhãn lean (B2-3)" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Bài mẫu (AC14)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Checklist AC14" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -471,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ngày: 2026-10-18. Branch agent/claude/b2-4-tarot-voice-versions. Chỉ dữ liệu tổng hợp.</t>
+          <t>Ngày: 2026-10-18. Branch agent/claude/b2-4b-tarot-provenance. Chỉ dữ liệu tổng hợp. B2-4b viết lại 6 tiêu đề (xem task doc).</t>
         </is>
       </c>
     </row>
@@ -536,33 +537,754 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Sheet 'Bài mẫu' (AC14): đọc cả bài và đánh giá theo checklist tâm lý của chuẩn nội dung:</t>
+          <t>Sheet 'Bài mẫu' (AC14): đọc cả bài; chấm ở sheet 'Checklist AC14' (cột 'Owner:' nền vàng, ghi Đạt/Chưa).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Cột 'Máy:' là kết quả tự động; map 'vòng lặp' có 2 và 'lựa chọn' có 3 ý điểm vướng/cái giá do cấu trúc map — cần owner quyết.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>không phán thay, không dự đoán, không đoán ý người khác, không đổ lỗi, có một bước nhỏ làm được, giọng tử tế.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Sau khi owner duyệt: Claude cập nhật câu, đưa question_frame.py, roles.py, stance.py, variants.py</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Sau khi owner duyệt: Claude cập nhật câu, đưa question_frame.py, roles.py, stance.py, variants.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>vào phạm vi fallback-approval.json và làm mới file đó trong PR phát hành (không làm trước khi có duyệt).</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Giọng</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Máy: tiêu đề có lời khuyên</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Máy: có ép buộc</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Máy: kết ở việc nhỏ</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Máy: số ý điểm vướng/cái giá</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Máy: cảnh có từ khuyên</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Máy: việc nhỏ có 'khi…'</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Owner: có căn cứ riêng (lá, vai, câu hỏi)</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Owner: không quyết thay / dự đoán / đoán ý</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Owner: tối đa 1 ý tiêu cực, có lối ra</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Owner: cảnh không khuyên</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Owner: Cà khịa trêu tình huống, không trêu người</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Duyệt (OK / Sửa / Bỏ)</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Góp ý của owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>playful_grounded</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>three_unblock</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>roast</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>three_unblock</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>playful_grounded</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>five_choice</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>roast</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>five_choice</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>playful_grounded</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>five_clarity</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>roast</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>five_clarity</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>playful_grounded</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>five_loop</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>roast</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>five_loop</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>playful_grounded</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>five_conversation</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>roast</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>five_conversation</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>playful_grounded</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>one_focus</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>roast</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>one_focus</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3543,12 +4265,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Với {focal}, nên cân nhắc thêm trước khi {action}.</t>
+          <t>{focal} cho thấy: cân nhắc thêm trước khi {action}.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Khoan đạp ga, {focal} bảo cân nhắc thêm trước khi {action}.</t>
+          <t>{focal} bật đèn vàng: cân nhắc thêm trước khi {action}.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3577,7 +4299,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>{focal}: cân nhắc thêm trước khi {action}, đừng vội nha.</t>
+          <t>{focal} giơ biển chậm lại: cân nhắc thêm trước khi {action}.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -3693,7 +4415,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>{pair}: khoan chọn vội, xem điều cần rõ trước khi chọn.</t>
+          <t>{pair} còn giằng co: có điều cần rõ trước khi chọn.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -3717,7 +4439,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Với {pair}, xem điều cần rõ trước khi chọn.</t>
+          <t>Với {pair}, có điều cần rõ trước khi chọn.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -3751,7 +4473,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>{pair}: điều cần rõ trước khi chọn, rồi hẵng tính.</t>
+          <t>{pair}: điều cần rõ trước khi chọn nằm ở đây.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
